--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9755,0.0089,0.0119,0.0009</t>
-  </si>
-  <si>
-    <t>0.9775,0.0030,0.0049,0.0036</t>
-  </si>
-  <si>
-    <t>0.9394,0.0222,0.0255,0.0047</t>
-  </si>
-  <si>
-    <t>0.9715,0.0050,0.0045,0.0042</t>
-  </si>
-  <si>
-    <t>0.9874,0.0011,0.0006,0.0035</t>
-  </si>
-  <si>
-    <t>0.8995,0.0134,0.0071,0.0449</t>
-  </si>
-  <si>
-    <t>0.9843,0.0019,0.0031,0.0049</t>
-  </si>
-  <si>
-    <t>0.9734,0.0050,0.0037,0.0058</t>
-  </si>
-  <si>
-    <t>0.9757,0.0015,0.0015,0.0113</t>
-  </si>
-  <si>
-    <t>0.9790,0.0038,0.0020,0.0039</t>
-  </si>
-  <si>
-    <t>0.9722,0.0024,0.0016,0.0122</t>
-  </si>
-  <si>
-    <t>0.9812,0.0036,0.0025,0.0037</t>
-  </si>
-  <si>
-    <t>0.9822,0.0039,0.0173,0.0005</t>
-  </si>
-  <si>
-    <t>0.9665,0.0098,0.0263,0.0017</t>
-  </si>
-  <si>
-    <t>0.9471,0.0157,0.0492,0.0015</t>
-  </si>
-  <si>
-    <t>0.8774,0.0028,0.2943,0.0002</t>
-  </si>
-  <si>
-    <t>0.9796,0.0070,0.0092,0.0010</t>
-  </si>
-  <si>
-    <t>0.9397,0.0580,0.0089,0.0009</t>
-  </si>
-  <si>
-    <t>0.9438,0.0320,0.0133,0.0026</t>
-  </si>
-  <si>
-    <t>0.9495,0.0230,0.0207,0.0046</t>
-  </si>
-  <si>
-    <t>0.5473,0.4262,0.0528,0.0055</t>
-  </si>
-  <si>
-    <t>0.8667,0.1010,0.0388,0.0058</t>
-  </si>
-  <si>
-    <t>0.9259,0.0057,0.1175,0.0008</t>
-  </si>
-  <si>
-    <t>0.9113,0.0123,0.1422,0.0002</t>
-  </si>
-  <si>
-    <t>0.9533,0.0020,0.1277,0.0003</t>
-  </si>
-  <si>
-    <t>0.9578,0.0037,0.0528,0.0003</t>
-  </si>
-  <si>
-    <t>0.9460,0.0052,0.0737,0.0005</t>
-  </si>
-  <si>
-    <t>0.8493,0.0055,0.3003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9520,0.0051,0.0854,0.0002</t>
-  </si>
-  <si>
-    <t>0.9458,0.0277,0.0137,0.0034</t>
-  </si>
-  <si>
-    <t>0.9809,0.0061,0.0067,0.0010</t>
-  </si>
-  <si>
-    <t>0.0670,0.0572,0.9564,0.0018</t>
-  </si>
-  <si>
-    <t>0.7280,0.0692,0.1858,0.0014</t>
-  </si>
-  <si>
-    <t>0.9428,0.0343,0.0093,0.0025</t>
-  </si>
-  <si>
-    <t>0.9934,0.0025,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9487,0.0483,0.0079,0.0014</t>
-  </si>
-  <si>
-    <t>0.9721,0.0168,0.0071,0.0013</t>
-  </si>
-  <si>
-    <t>0.8055,0.0352,0.2304,0.0004</t>
-  </si>
-  <si>
-    <t>0.9410,0.0011,0.1985,0.0001</t>
-  </si>
-  <si>
-    <t>0.9376,0.0012,0.2115,0.0000</t>
-  </si>
-  <si>
-    <t>0.9431,0.0024,0.1398,0.0001</t>
-  </si>
-  <si>
-    <t>0.8725,0.0015,0.3459,0.0001</t>
-  </si>
-  <si>
-    <t>0.1713,0.3933,0.2092,0.0003</t>
-  </si>
-  <si>
-    <t>0.5461,0.0091,0.5919,0.0003</t>
-  </si>
-  <si>
-    <t>0.9444,0.0229,0.0237,0.0036</t>
-  </si>
-  <si>
-    <t>0.1294,0.8776,0.0539,0.0025</t>
-  </si>
-  <si>
-    <t>0.9478,0.0479,0.0118,0.0006</t>
-  </si>
-  <si>
-    <t>0.1692,0.6566,0.3945,0.0066</t>
-  </si>
-  <si>
-    <t>0.2810,0.0052,0.9134,0.0001</t>
-  </si>
-  <si>
-    <t>0.3135,0.0072,0.8633,0.0001</t>
-  </si>
-  <si>
-    <t>0.6503,0.0213,0.4780,0.0004</t>
-  </si>
-  <si>
-    <t>0.8841,0.0034,0.2541,0.0003</t>
-  </si>
-  <si>
-    <t>0.2356,0.0076,0.9234,0.0003</t>
-  </si>
-  <si>
-    <t>0.8687,0.0048,0.2720,0.0001</t>
-  </si>
-  <si>
-    <t>0.9737,0.0041,0.0074,0.0100</t>
-  </si>
-  <si>
-    <t>0.9841,0.0027,0.0024,0.0037</t>
-  </si>
-  <si>
-    <t>0.9070,0.0387,0.0225,0.0171</t>
-  </si>
-  <si>
-    <t>0.5265,0.0230,0.5695,0.0097</t>
-  </si>
-  <si>
-    <t>0.9808,0.0016,0.0017,0.0078</t>
-  </si>
-  <si>
-    <t>0.9660,0.0042,0.0043,0.0109</t>
-  </si>
-  <si>
-    <t>0.9896,0.0031,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.4416,0.0486,0.6520,0.0000</t>
-  </si>
-  <si>
-    <t>0.4116,0.0049,0.8460,0.0000</t>
-  </si>
-  <si>
-    <t>0.8573,0.0047,0.3164,0.0001</t>
-  </si>
-  <si>
-    <t>0.1984,0.0590,0.8597,0.0000</t>
-  </si>
-  <si>
-    <t>0.2959,0.0018,0.9152,0.0000</t>
-  </si>
-  <si>
-    <t>0.9686,0.0209,0.0107,0.0005</t>
-  </si>
-  <si>
-    <t>0.3563,0.7201,0.0098,0.0001</t>
-  </si>
-  <si>
-    <t>0.9651,0.0187,0.0102,0.0024</t>
-  </si>
-  <si>
-    <t>0.9725,0.0059,0.0122,0.0024</t>
-  </si>
-  <si>
-    <t>0.0855,0.0752,0.8554,0.0037</t>
-  </si>
-  <si>
-    <t>0.2873,0.1497,0.6963,0.0006</t>
-  </si>
-  <si>
-    <t>0.2813,0.1449,0.6893,0.0002</t>
-  </si>
-  <si>
-    <t>0.1166,0.3998,0.6505,0.0001</t>
-  </si>
-  <si>
-    <t>0.1346,0.4912,0.7080,0.0003</t>
-  </si>
-  <si>
-    <t>0.9435,0.0087,0.0210,0.0104</t>
-  </si>
-  <si>
-    <t>0.9715,0.0019,0.0062,0.0061</t>
-  </si>
-  <si>
-    <t>0.9686,0.0028,0.0031,0.0116</t>
-  </si>
-  <si>
-    <t>0.9408,0.0224,0.0126,0.0135</t>
-  </si>
-  <si>
-    <t>0.9411,0.0156,0.0333,0.0103</t>
-  </si>
-  <si>
-    <t>0.9505,0.0099,0.0075,0.0142</t>
-  </si>
-  <si>
-    <t>0.1626,0.2295,0.6271,0.0001</t>
-  </si>
-  <si>
-    <t>0.1911,0.0606,0.9108,0.0001</t>
-  </si>
-  <si>
-    <t>0.2789,0.1142,0.5392,0.0002</t>
-  </si>
-  <si>
-    <t>0.9187,0.0107,0.1050,0.0001</t>
-  </si>
-  <si>
-    <t>0.1772,0.0893,0.7019,0.0000</t>
-  </si>
-  <si>
-    <t>0.3294,0.2726,0.3142,0.0001</t>
-  </si>
-  <si>
-    <t>0.9844,0.0036,0.0042,0.0018</t>
-  </si>
-  <si>
-    <t>0.9426,0.0162,0.0095,0.0093</t>
-  </si>
-  <si>
-    <t>0.9842,0.0028,0.0013,0.0030</t>
-  </si>
-  <si>
-    <t>0.9646,0.0031,0.0057,0.0166</t>
-  </si>
-  <si>
-    <t>0.9854,0.0025,0.0020,0.0023</t>
-  </si>
-  <si>
-    <t>0.9737,0.0045,0.0055,0.0043</t>
-  </si>
-  <si>
-    <t>0.8995,0.0326,0.0210,0.0212</t>
-  </si>
-  <si>
-    <t>0.9384,0.0222,0.0145,0.0096</t>
-  </si>
-  <si>
-    <t>0.9510,0.0043,0.0024,0.0229</t>
-  </si>
-  <si>
-    <t>0.9762,0.0042,0.0018,0.0044</t>
-  </si>
-  <si>
-    <t>0.9574,0.0056,0.0054,0.0167</t>
-  </si>
-  <si>
-    <t>0.9793,0.0016,0.0011,0.0070</t>
-  </si>
-  <si>
-    <t>0.9872,0.0014,0.0027,0.0030</t>
-  </si>
-  <si>
-    <t>0.9887,0.0016,0.0023,0.0023</t>
-  </si>
-  <si>
-    <t>0.9870,0.0013,0.0015,0.0055</t>
-  </si>
-  <si>
-    <t>0.9570,0.0038,0.0077,0.0261</t>
-  </si>
-  <si>
-    <t>0.8182,0.0032,0.4040,0.0003</t>
-  </si>
-  <si>
-    <t>0.9331,0.0065,0.1059,0.0004</t>
-  </si>
-  <si>
-    <t>0.9804,0.0045,0.0173,0.0004</t>
-  </si>
-  <si>
-    <t>0.9338,0.0402,0.0112,0.0003</t>
-  </si>
-  <si>
-    <t>0.8965,0.0815,0.0181,0.0058</t>
-  </si>
-  <si>
-    <t>0.9642,0.0171,0.0076,0.0024</t>
-  </si>
-  <si>
-    <t>0.9836,0.0075,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.9460,0.0187,0.0176,0.0064</t>
-  </si>
-  <si>
-    <t>0.9132,0.0951,0.0092,0.0007</t>
-  </si>
-  <si>
-    <t>0.5546,0.5495,0.0455,0.0068</t>
-  </si>
-  <si>
-    <t>0.9821,0.0072,0.0075,0.0008</t>
-  </si>
-  <si>
-    <t>0.9668,0.0086,0.0161,0.0026</t>
-  </si>
-  <si>
-    <t>0.9474,0.0043,0.1131,0.0007</t>
-  </si>
-  <si>
-    <t>0.8312,0.0318,0.1576,0.0020</t>
-  </si>
-  <si>
-    <t>0.9841,0.0029,0.0256,0.0003</t>
-  </si>
-  <si>
-    <t>0.8303,0.0780,0.0816,0.0391</t>
-  </si>
-  <si>
-    <t>0.5785,0.4377,0.0551,0.0012</t>
-  </si>
-  <si>
-    <t>0.5611,0.4372,0.0374,0.0014</t>
-  </si>
-  <si>
-    <t>0.9093,0.0428,0.0407,0.0028</t>
-  </si>
-  <si>
-    <t>0.0606,0.3776,0.9092,0.0027</t>
-  </si>
-  <si>
-    <t>0.8907,0.0871,0.0367,0.0017</t>
-  </si>
-  <si>
-    <t>0.9676,0.0078,0.0103,0.0042</t>
-  </si>
-  <si>
-    <t>0.9552,0.0229,0.0148,0.0022</t>
-  </si>
-  <si>
-    <t>0.9848,0.0014,0.0029,0.0039</t>
-  </si>
-  <si>
-    <t>0.9361,0.0192,0.0111,0.0124</t>
-  </si>
-  <si>
-    <t>0.9660,0.0038,0.0034,0.0128</t>
-  </si>
-  <si>
-    <t>0.9893,0.0015,0.0022,0.0016</t>
-  </si>
-  <si>
-    <t>0.9702,0.0037,0.0018,0.0089</t>
-  </si>
-  <si>
-    <t>0.9859,0.0019,0.0072,0.0023</t>
-  </si>
-  <si>
-    <t>0.9797,0.0049,0.0031,0.0036</t>
-  </si>
-  <si>
-    <t>0.9305,0.0148,0.0209,0.0161</t>
-  </si>
-  <si>
-    <t>0.8034,0.0021,0.5276,0.0001</t>
-  </si>
-  <si>
-    <t>0.9048,0.0186,0.0751,0.0001</t>
-  </si>
-  <si>
-    <t>0.5113,0.0159,0.6120,0.0001</t>
-  </si>
-  <si>
-    <t>0.7736,0.0101,0.3631,0.0002</t>
-  </si>
-  <si>
-    <t>0.9912,0.0024,0.0067,0.0002</t>
-  </si>
-  <si>
-    <t>0.9751,0.0064,0.0110,0.0017</t>
-  </si>
-  <si>
-    <t>0.9147,0.0086,0.1537,0.0029</t>
-  </si>
-  <si>
-    <t>0.9710,0.0060,0.0322,0.0006</t>
-  </si>
-  <si>
-    <t>0.9648,0.0036,0.0122,0.0056</t>
-  </si>
-  <si>
-    <t>0.6167,0.0144,0.0102,0.3398</t>
-  </si>
-  <si>
-    <t>0.9765,0.0026,0.0042,0.0052</t>
-  </si>
-  <si>
-    <t>0.9398,0.0042,0.0199,0.0155</t>
-  </si>
-  <si>
-    <t>0.0230,0.4570,0.9556,0.0003</t>
-  </si>
-  <si>
-    <t>0.9636,0.0118,0.0062,0.0044</t>
-  </si>
-  <si>
-    <t>0.9598,0.0221,0.0191,0.0027</t>
-  </si>
-  <si>
-    <t>0.9358,0.0211,0.0104,0.0118</t>
-  </si>
-  <si>
-    <t>0.9097,0.0555,0.0069,0.0048</t>
-  </si>
-  <si>
-    <t>0.9674,0.0046,0.0047,0.0099</t>
-  </si>
-  <si>
-    <t>0.9761,0.0020,0.0055,0.0062</t>
-  </si>
-  <si>
-    <t>0.8932,0.0200,0.0046,0.0278</t>
-  </si>
-  <si>
-    <t>0.0528,0.0838,0.9485,0.0093</t>
-  </si>
-  <si>
-    <t>0.9589,0.0116,0.0067,0.0039</t>
-  </si>
-  <si>
-    <t>0.8702,0.0186,0.0426,0.0442</t>
-  </si>
-  <si>
-    <t>0.9594,0.0146,0.0160,0.0037</t>
-  </si>
-  <si>
-    <t>0.9563,0.0208,0.0221,0.0018</t>
-  </si>
-  <si>
-    <t>0.9899,0.0017,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.9652,0.0080,0.0319,0.0015</t>
-  </si>
-  <si>
-    <t>0.9881,0.0044,0.0040,0.0006</t>
-  </si>
-  <si>
-    <t>0.9874,0.0049,0.0044,0.0005</t>
-  </si>
-  <si>
-    <t>0.9712,0.0040,0.0066,0.0070</t>
-  </si>
-  <si>
-    <t>0.9626,0.0103,0.0046,0.0052</t>
-  </si>
-  <si>
-    <t>0.9596,0.0120,0.0065,0.0078</t>
-  </si>
-  <si>
-    <t>0.9863,0.0027,0.0039,0.0016</t>
-  </si>
-  <si>
-    <t>0.9704,0.0061,0.0034,0.0057</t>
-  </si>
-  <si>
-    <t>0.9377,0.0038,0.0036,0.0364</t>
-  </si>
-  <si>
-    <t>0.9796,0.0019,0.0014,0.0070</t>
-  </si>
-  <si>
-    <t>0.9797,0.0031,0.0024,0.0037</t>
-  </si>
-  <si>
-    <t>0.9174,0.0481,0.0189,0.0089</t>
-  </si>
-  <si>
-    <t>0.9542,0.0140,0.0138,0.0063</t>
-  </si>
-  <si>
-    <t>0.9165,0.0289,0.0266,0.0092</t>
-  </si>
-  <si>
-    <t>0.9766,0.0052,0.0046,0.0031</t>
-  </si>
-  <si>
-    <t>0.9258,0.0346,0.0100,0.0064</t>
-  </si>
-  <si>
-    <t>0.9776,0.0047,0.0063,0.0036</t>
-  </si>
-  <si>
-    <t>0.9710,0.0131,0.0049,0.0028</t>
-  </si>
-  <si>
-    <t>0.9721,0.0054,0.0076,0.0049</t>
-  </si>
-  <si>
-    <t>0.0484,0.0243,0.9791,0.0008</t>
-  </si>
-  <si>
-    <t>0.9761,0.0046,0.0063,0.0027</t>
-  </si>
-  <si>
-    <t>0.6594,0.0039,0.5418,0.0001</t>
-  </si>
-  <si>
-    <t>0.8856,0.0057,0.3651,0.0005</t>
-  </si>
-  <si>
-    <t>0.9120,0.0035,0.1797,0.0007</t>
-  </si>
-  <si>
-    <t>0.8632,0.0089,0.2531,0.0001</t>
-  </si>
-  <si>
-    <t>0.9499,0.0096,0.0700,0.0002</t>
-  </si>
-  <si>
-    <t>0.5937,0.0040,0.6390,0.0002</t>
-  </si>
-  <si>
-    <t>0.2607,0.0146,0.8721,0.0004</t>
-  </si>
-  <si>
-    <t>0.8994,0.0406,0.0675,0.0016</t>
-  </si>
-  <si>
-    <t>0.7168,0.0218,0.3935,0.0017</t>
-  </si>
-  <si>
-    <t>0.9568,0.0124,0.0331,0.0011</t>
-  </si>
-  <si>
-    <t>0.9035,0.0131,0.1056,0.0010</t>
-  </si>
-  <si>
-    <t>0.9636,0.0137,0.0177,0.0006</t>
-  </si>
-  <si>
-    <t>0.9348,0.0290,0.0362,0.0007</t>
-  </si>
-  <si>
-    <t>0.9453,0.0246,0.0274,0.0018</t>
-  </si>
-  <si>
-    <t>0.9731,0.0060,0.0190,0.0018</t>
-  </si>
-  <si>
-    <t>0.8723,0.0877,0.0074,0.0078</t>
-  </si>
-  <si>
-    <t>0.8905,0.0435,0.0131,0.0141</t>
-  </si>
-  <si>
-    <t>0.9793,0.0057,0.0033,0.0025</t>
-  </si>
-  <si>
-    <t>0.9857,0.0027,0.0016,0.0020</t>
-  </si>
-  <si>
-    <t>0.9578,0.0252,0.0047,0.0033</t>
-  </si>
-  <si>
-    <t>0.9595,0.0151,0.0149,0.0017</t>
-  </si>
-  <si>
-    <t>0.9478,0.0051,0.0815,0.0028</t>
-  </si>
-  <si>
-    <t>0.9625,0.0101,0.0221,0.0017</t>
-  </si>
-  <si>
-    <t>0.9763,0.0030,0.0350,0.0003</t>
-  </si>
-  <si>
-    <t>0.9460,0.0109,0.0617,0.0025</t>
-  </si>
-  <si>
-    <t>0.9561,0.0077,0.0532,0.0007</t>
-  </si>
-  <si>
-    <t>0.8533,0.0027,0.3692,0.0001</t>
-  </si>
-  <si>
-    <t>0.9065,0.0074,0.1519,0.0000</t>
-  </si>
-  <si>
-    <t>0.7977,0.0095,0.2370,0.0001</t>
-  </si>
-  <si>
-    <t>0.5457,0.0422,0.4449,0.0002</t>
-  </si>
-  <si>
-    <t>0.9664,0.0070,0.0030,0.0066</t>
-  </si>
-  <si>
-    <t>0.9704,0.0056,0.0045,0.0052</t>
-  </si>
-  <si>
-    <t>0.9563,0.0066,0.0037,0.0144</t>
-  </si>
-  <si>
-    <t>0.9812,0.0021,0.0015,0.0049</t>
-  </si>
-  <si>
-    <t>0.9693,0.0114,0.0048,0.0029</t>
-  </si>
-  <si>
-    <t>0.9784,0.0087,0.0100,0.0025</t>
-  </si>
-  <si>
-    <t>0.9443,0.0065,0.0045,0.0242</t>
-  </si>
-  <si>
-    <t>0.9367,0.0188,0.0130,0.0127</t>
-  </si>
-  <si>
-    <t>0.9838,0.0047,0.0175,0.0007</t>
-  </si>
-  <si>
-    <t>0.9392,0.0203,0.0393,0.0035</t>
-  </si>
-  <si>
-    <t>0.9533,0.0150,0.0229,0.0032</t>
-  </si>
-  <si>
-    <t>0.4711,0.0022,0.7494,0.0002</t>
-  </si>
-  <si>
-    <t>0.1467,0.0176,0.9420,0.0002</t>
-  </si>
-  <si>
-    <t>0.8331,0.0209,0.2227,0.0003</t>
-  </si>
-  <si>
-    <t>0.0624,0.0144,0.9787,0.0001</t>
-  </si>
-  <si>
-    <t>0.9793,0.0042,0.0205,0.0003</t>
-  </si>
-  <si>
-    <t>0.1340,0.0066,0.9609,0.0001</t>
-  </si>
-  <si>
-    <t>0.9051,0.0100,0.1562,0.0002</t>
-  </si>
-  <si>
-    <t>0.9672,0.0070,0.0343,0.0005</t>
-  </si>
-  <si>
-    <t>0.9842,0.0028,0.0187,0.0004</t>
-  </si>
-  <si>
-    <t>0.9743,0.0021,0.0544,0.0004</t>
-  </si>
-  <si>
-    <t>0.9839,0.0035,0.0137,0.0006</t>
-  </si>
-  <si>
-    <t>0.9838,0.0050,0.0023,0.0017</t>
-  </si>
-  <si>
-    <t>0.9876,0.0013,0.0011,0.0038</t>
-  </si>
-  <si>
-    <t>0.9876,0.0027,0.0018,0.0020</t>
-  </si>
-  <si>
-    <t>0.9601,0.0051,0.0092,0.0146</t>
-  </si>
-  <si>
-    <t>0.9870,0.0018,0.0013,0.0031</t>
-  </si>
-  <si>
-    <t>0.9812,0.0028,0.0017,0.0049</t>
-  </si>
-  <si>
-    <t>0.9738,0.0041,0.0060,0.0059</t>
-  </si>
-  <si>
-    <t>0.9629,0.0075,0.0037,0.0111</t>
-  </si>
-  <si>
-    <t>0.7122,0.0201,0.4308,0.0004</t>
-  </si>
-  <si>
-    <t>0.1062,0.0192,0.9363,0.0002</t>
-  </si>
-  <si>
-    <t>0.1071,0.1795,0.7990,0.0007</t>
-  </si>
-  <si>
-    <t>0.8846,0.0090,0.2135,0.0004</t>
-  </si>
-  <si>
-    <t>0.8245,0.0011,0.4002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9581,0.0093,0.0421,0.0015</t>
-  </si>
-  <si>
-    <t>0.9685,0.0023,0.0582,0.0002</t>
-  </si>
-  <si>
-    <t>0.8819,0.0014,0.3101,0.0002</t>
-  </si>
-  <si>
-    <t>0.9331,0.0119,0.0212,0.0137</t>
-  </si>
-  <si>
-    <t>0.9413,0.0123,0.0337,0.0061</t>
-  </si>
-  <si>
-    <t>0.9343,0.0066,0.0140,0.0288</t>
-  </si>
-  <si>
-    <t>0.9099,0.0060,0.0196,0.0374</t>
-  </si>
-  <si>
-    <t>0.7587,0.0043,0.0144,0.2376</t>
-  </si>
-  <si>
-    <t>0.9919,0.0015,0.0021,0.0006</t>
+    <t>0.9451,0.0162,0.0428,0.0019</t>
+  </si>
+  <si>
+    <t>0.9127,0.0145,0.0275,0.0198</t>
+  </si>
+  <si>
+    <t>0.9827,0.0057,0.0053,0.0011</t>
+  </si>
+  <si>
+    <t>0.9768,0.0028,0.0052,0.0037</t>
+  </si>
+  <si>
+    <t>0.9692,0.0060,0.0025,0.0070</t>
+  </si>
+  <si>
+    <t>0.9649,0.0045,0.0024,0.0118</t>
+  </si>
+  <si>
+    <t>0.9829,0.0026,0.0017,0.0040</t>
+  </si>
+  <si>
+    <t>0.9805,0.0028,0.0028,0.0044</t>
+  </si>
+  <si>
+    <t>0.9798,0.0021,0.0013,0.0063</t>
+  </si>
+  <si>
+    <t>0.9752,0.0050,0.0036,0.0048</t>
+  </si>
+  <si>
+    <t>0.9851,0.0027,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9684,0.0093,0.0057,0.0045</t>
+  </si>
+  <si>
+    <t>0.9548,0.0145,0.0388,0.0004</t>
+  </si>
+  <si>
+    <t>0.9670,0.0053,0.0429,0.0007</t>
+  </si>
+  <si>
+    <t>0.9337,0.0123,0.1024,0.0016</t>
+  </si>
+  <si>
+    <t>0.9656,0.0098,0.0311,0.0008</t>
+  </si>
+  <si>
+    <t>0.9897,0.0027,0.0063,0.0004</t>
+  </si>
+  <si>
+    <t>0.9144,0.0949,0.0173,0.0013</t>
+  </si>
+  <si>
+    <t>0.8379,0.1790,0.0124,0.0036</t>
+  </si>
+  <si>
+    <t>0.9603,0.0258,0.0127,0.0021</t>
+  </si>
+  <si>
+    <t>0.8754,0.1277,0.0095,0.0023</t>
+  </si>
+  <si>
+    <t>0.9565,0.0295,0.0148,0.0012</t>
+  </si>
+  <si>
+    <t>0.9924,0.0017,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.9615,0.0042,0.0676,0.0001</t>
+  </si>
+  <si>
+    <t>0.8749,0.0064,0.2794,0.0006</t>
+  </si>
+  <si>
+    <t>0.9413,0.0061,0.0915,0.0006</t>
+  </si>
+  <si>
+    <t>0.9221,0.0020,0.1854,0.0002</t>
+  </si>
+  <si>
+    <t>0.9497,0.0050,0.0769,0.0005</t>
+  </si>
+  <si>
+    <t>0.6934,0.0083,0.5275,0.0005</t>
+  </si>
+  <si>
+    <t>0.9848,0.0049,0.0083,0.0006</t>
+  </si>
+  <si>
+    <t>0.9589,0.0185,0.0125,0.0021</t>
+  </si>
+  <si>
+    <t>0.1912,0.0250,0.9312,0.0003</t>
+  </si>
+  <si>
+    <t>0.9135,0.0335,0.0473,0.0010</t>
+  </si>
+  <si>
+    <t>0.9649,0.0192,0.0097,0.0019</t>
+  </si>
+  <si>
+    <t>0.9794,0.0058,0.0039,0.0019</t>
+  </si>
+  <si>
+    <t>0.9228,0.0397,0.0242,0.0046</t>
+  </si>
+  <si>
+    <t>0.9824,0.0089,0.0056,0.0008</t>
+  </si>
+  <si>
+    <t>0.9503,0.0115,0.0245,0.0000</t>
+  </si>
+  <si>
+    <t>0.9837,0.0002,0.0738,0.0000</t>
+  </si>
+  <si>
+    <t>0.7101,0.0036,0.6027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9394,0.0031,0.1620,0.0002</t>
+  </si>
+  <si>
+    <t>0.7218,0.0117,0.4125,0.0002</t>
+  </si>
+  <si>
+    <t>0.7503,0.0602,0.1265,0.0001</t>
+  </si>
+  <si>
+    <t>0.9461,0.0036,0.1189,0.0005</t>
+  </si>
+  <si>
+    <t>0.9297,0.0419,0.0147,0.0062</t>
+  </si>
+  <si>
+    <t>0.2267,0.7898,0.1488,0.0061</t>
+  </si>
+  <si>
+    <t>0.1808,0.8001,0.1215,0.0019</t>
+  </si>
+  <si>
+    <t>0.2441,0.7479,0.2155,0.0134</t>
+  </si>
+  <si>
+    <t>0.2595,0.0133,0.8075,0.0001</t>
+  </si>
+  <si>
+    <t>0.7309,0.0109,0.4991,0.0002</t>
+  </si>
+  <si>
+    <t>0.9810,0.0022,0.0319,0.0001</t>
+  </si>
+  <si>
+    <t>0.8087,0.0027,0.3845,0.0001</t>
+  </si>
+  <si>
+    <t>0.1248,0.0267,0.9015,0.0005</t>
+  </si>
+  <si>
+    <t>0.8717,0.0059,0.2105,0.0004</t>
+  </si>
+  <si>
+    <t>0.9290,0.0296,0.0094,0.0096</t>
+  </si>
+  <si>
+    <t>0.9734,0.0055,0.0072,0.0046</t>
+  </si>
+  <si>
+    <t>0.9502,0.0175,0.0080,0.0071</t>
+  </si>
+  <si>
+    <t>0.6666,0.0447,0.4731,0.0065</t>
+  </si>
+  <si>
+    <t>0.9672,0.0028,0.0051,0.0141</t>
+  </si>
+  <si>
+    <t>0.9131,0.0186,0.0108,0.0213</t>
+  </si>
+  <si>
+    <t>0.9844,0.0038,0.0010,0.0020</t>
+  </si>
+  <si>
+    <t>0.1625,0.0185,0.9306,0.0002</t>
+  </si>
+  <si>
+    <t>0.8167,0.0028,0.4295,0.0001</t>
+  </si>
+  <si>
+    <t>0.8259,0.0246,0.2785,0.0005</t>
+  </si>
+  <si>
+    <t>0.0240,0.3554,0.9612,0.0001</t>
+  </si>
+  <si>
+    <t>0.6928,0.0034,0.5415,0.0001</t>
+  </si>
+  <si>
+    <t>0.9513,0.0277,0.0148,0.0003</t>
+  </si>
+  <si>
+    <t>0.3284,0.7790,0.0104,0.0002</t>
+  </si>
+  <si>
+    <t>0.9608,0.0121,0.0233,0.0034</t>
+  </si>
+  <si>
+    <t>0.9745,0.0041,0.0118,0.0026</t>
+  </si>
+  <si>
+    <t>0.1557,0.0606,0.8066,0.0026</t>
+  </si>
+  <si>
+    <t>0.7425,0.0366,0.2419,0.0001</t>
+  </si>
+  <si>
+    <t>0.7580,0.0124,0.4850,0.0000</t>
+  </si>
+  <si>
+    <t>0.0615,0.7370,0.6980,0.0001</t>
+  </si>
+  <si>
+    <t>0.1078,0.0717,0.9041,0.0000</t>
+  </si>
+  <si>
+    <t>0.9561,0.0052,0.0177,0.0082</t>
+  </si>
+  <si>
+    <t>0.9325,0.0045,0.0040,0.0386</t>
+  </si>
+  <si>
+    <t>0.9785,0.0030,0.0019,0.0046</t>
+  </si>
+  <si>
+    <t>0.9761,0.0042,0.0037,0.0051</t>
+  </si>
+  <si>
+    <t>0.9751,0.0031,0.0081,0.0045</t>
+  </si>
+  <si>
+    <t>0.9793,0.0026,0.0037,0.0065</t>
+  </si>
+  <si>
+    <t>0.7624,0.0558,0.2232,0.0002</t>
+  </si>
+  <si>
+    <t>0.1643,0.0077,0.9423,0.0000</t>
+  </si>
+  <si>
+    <t>0.1779,0.0408,0.8777,0.0001</t>
+  </si>
+  <si>
+    <t>0.5767,0.0270,0.5607,0.0001</t>
+  </si>
+  <si>
+    <t>0.5079,0.0222,0.5848,0.0000</t>
+  </si>
+  <si>
+    <t>0.7365,0.0798,0.1034,0.0004</t>
+  </si>
+  <si>
+    <t>0.9917,0.0007,0.0009,0.0023</t>
+  </si>
+  <si>
+    <t>0.9566,0.0098,0.0034,0.0097</t>
+  </si>
+  <si>
+    <t>0.9645,0.0072,0.0048,0.0063</t>
+  </si>
+  <si>
+    <t>0.9859,0.0030,0.0024,0.0027</t>
+  </si>
+  <si>
+    <t>0.9904,0.0010,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.9497,0.0136,0.0126,0.0131</t>
+  </si>
+  <si>
+    <t>0.9880,0.0021,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.9772,0.0070,0.0052,0.0028</t>
+  </si>
+  <si>
+    <t>0.9908,0.0010,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.9600,0.0075,0.0068,0.0116</t>
+  </si>
+  <si>
+    <t>0.9756,0.0020,0.0015,0.0120</t>
+  </si>
+  <si>
+    <t>0.9889,0.0008,0.0006,0.0041</t>
+  </si>
+  <si>
+    <t>0.9696,0.0028,0.0020,0.0130</t>
+  </si>
+  <si>
+    <t>0.9715,0.0032,0.0016,0.0090</t>
+  </si>
+  <si>
+    <t>0.9858,0.0011,0.0013,0.0053</t>
+  </si>
+  <si>
+    <t>0.9773,0.0039,0.0030,0.0062</t>
+  </si>
+  <si>
+    <t>0.7984,0.0041,0.4533,0.0004</t>
+  </si>
+  <si>
+    <t>0.8978,0.0081,0.1541,0.0003</t>
+  </si>
+  <si>
+    <t>0.9806,0.0052,0.0140,0.0002</t>
+  </si>
+  <si>
+    <t>0.8977,0.0120,0.1146,0.0007</t>
+  </si>
+  <si>
+    <t>0.9255,0.0642,0.0069,0.0023</t>
+  </si>
+  <si>
+    <t>0.8698,0.1591,0.0085,0.0024</t>
+  </si>
+  <si>
+    <t>0.9537,0.0153,0.0175,0.0045</t>
+  </si>
+  <si>
+    <t>0.9598,0.0244,0.0145,0.0012</t>
+  </si>
+  <si>
+    <t>0.7552,0.3191,0.0136,0.0017</t>
+  </si>
+  <si>
+    <t>0.5922,0.4458,0.0212,0.0014</t>
+  </si>
+  <si>
+    <t>0.9592,0.0169,0.0041,0.0032</t>
+  </si>
+  <si>
+    <t>0.9747,0.0039,0.0344,0.0006</t>
+  </si>
+  <si>
+    <t>0.9386,0.0074,0.0846,0.0011</t>
+  </si>
+  <si>
+    <t>0.9499,0.0216,0.0290,0.0007</t>
+  </si>
+  <si>
+    <t>0.8241,0.0581,0.1378,0.0064</t>
+  </si>
+  <si>
+    <t>0.9727,0.0021,0.0132,0.0029</t>
+  </si>
+  <si>
+    <t>0.6596,0.3078,0.1185,0.0063</t>
+  </si>
+  <si>
+    <t>0.7261,0.2030,0.0601,0.0016</t>
+  </si>
+  <si>
+    <t>0.8136,0.1157,0.0886,0.0116</t>
+  </si>
+  <si>
+    <t>0.0385,0.6706,0.8576,0.0012</t>
+  </si>
+  <si>
+    <t>0.9601,0.0170,0.0074,0.0041</t>
+  </si>
+  <si>
+    <t>0.9672,0.0152,0.0073,0.0018</t>
+  </si>
+  <si>
+    <t>0.9184,0.0327,0.0183,0.0122</t>
+  </si>
+  <si>
+    <t>0.9784,0.0049,0.0059,0.0023</t>
+  </si>
+  <si>
+    <t>0.9813,0.0042,0.0043,0.0039</t>
+  </si>
+  <si>
+    <t>0.9755,0.0044,0.0104,0.0052</t>
+  </si>
+  <si>
+    <t>0.9439,0.0082,0.0126,0.0192</t>
+  </si>
+  <si>
+    <t>0.9858,0.0021,0.0031,0.0025</t>
+  </si>
+  <si>
+    <t>0.9803,0.0032,0.0045,0.0031</t>
+  </si>
+  <si>
+    <t>0.9720,0.0037,0.0052,0.0088</t>
+  </si>
+  <si>
+    <t>0.9698,0.0060,0.0033,0.0057</t>
+  </si>
+  <si>
+    <t>0.5198,0.0527,0.5945,0.0015</t>
+  </si>
+  <si>
+    <t>0.4266,0.0228,0.7642,0.0001</t>
+  </si>
+  <si>
+    <t>0.9726,0.0020,0.0854,0.0000</t>
+  </si>
+  <si>
+    <t>0.7236,0.0038,0.5846,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0009,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.9697,0.0106,0.0129,0.0017</t>
+  </si>
+  <si>
+    <t>0.9942,0.0005,0.0115,0.0001</t>
+  </si>
+  <si>
+    <t>0.9178,0.0228,0.0713,0.0021</t>
+  </si>
+  <si>
+    <t>0.9680,0.0033,0.0084,0.0069</t>
+  </si>
+  <si>
+    <t>0.7014,0.0088,0.0281,0.2438</t>
+  </si>
+  <si>
+    <t>0.9400,0.0108,0.0078,0.0188</t>
+  </si>
+  <si>
+    <t>0.9672,0.0033,0.0097,0.0060</t>
+  </si>
+  <si>
+    <t>0.0715,0.6160,0.6191,0.0015</t>
+  </si>
+  <si>
+    <t>0.9717,0.0056,0.0056,0.0045</t>
+  </si>
+  <si>
+    <t>0.8547,0.0878,0.0547,0.0098</t>
+  </si>
+  <si>
+    <t>0.9769,0.0041,0.0108,0.0031</t>
+  </si>
+  <si>
+    <t>0.9549,0.0255,0.0051,0.0033</t>
+  </si>
+  <si>
+    <t>0.9815,0.0060,0.0079,0.0018</t>
+  </si>
+  <si>
+    <t>0.9475,0.0113,0.0057,0.0078</t>
+  </si>
+  <si>
+    <t>0.9625,0.0089,0.0152,0.0044</t>
+  </si>
+  <si>
+    <t>0.2031,0.0182,0.8449,0.0074</t>
+  </si>
+  <si>
+    <t>0.9413,0.0078,0.0113,0.0135</t>
+  </si>
+  <si>
+    <t>0.8700,0.0340,0.1051,0.0169</t>
+  </si>
+  <si>
+    <t>0.9664,0.0133,0.0170,0.0020</t>
+  </si>
+  <si>
+    <t>0.9654,0.0185,0.0086,0.0012</t>
+  </si>
+  <si>
+    <t>0.9809,0.0053,0.0113,0.0010</t>
+  </si>
+  <si>
+    <t>0.9661,0.0116,0.0231,0.0009</t>
+  </si>
+  <si>
+    <t>0.9318,0.0297,0.0371,0.0032</t>
+  </si>
+  <si>
+    <t>0.9785,0.0099,0.0107,0.0003</t>
+  </si>
+  <si>
+    <t>0.9860,0.0023,0.0019,0.0029</t>
+  </si>
+  <si>
+    <t>0.9599,0.0079,0.0057,0.0105</t>
+  </si>
+  <si>
+    <t>0.9865,0.0016,0.0025,0.0024</t>
+  </si>
+  <si>
+    <t>0.9532,0.0108,0.0035,0.0076</t>
+  </si>
+  <si>
+    <t>0.9736,0.0059,0.0097,0.0038</t>
+  </si>
+  <si>
+    <t>0.9657,0.0067,0.0051,0.0058</t>
+  </si>
+  <si>
+    <t>0.9830,0.0031,0.0044,0.0025</t>
+  </si>
+  <si>
+    <t>0.9733,0.0020,0.0029,0.0129</t>
+  </si>
+  <si>
+    <t>0.9499,0.0356,0.0118,0.0014</t>
+  </si>
+  <si>
+    <t>0.9501,0.0199,0.0121,0.0053</t>
+  </si>
+  <si>
+    <t>0.9793,0.0075,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.9302,0.0177,0.0780,0.0052</t>
+  </si>
+  <si>
+    <t>0.9634,0.0090,0.0106,0.0052</t>
+  </si>
+  <si>
+    <t>0.9837,0.0025,0.0025,0.0028</t>
+  </si>
+  <si>
+    <t>0.9904,0.0022,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9711,0.0056,0.0056,0.0051</t>
+  </si>
+  <si>
+    <t>0.0198,0.0075,0.9909,0.0010</t>
+  </si>
+  <si>
+    <t>0.9600,0.0083,0.0111,0.0083</t>
+  </si>
+  <si>
+    <t>0.3440,0.0085,0.8003,0.0005</t>
+  </si>
+  <si>
+    <t>0.7345,0.0026,0.5414,0.0005</t>
+  </si>
+  <si>
+    <t>0.8912,0.0093,0.1774,0.0004</t>
+  </si>
+  <si>
+    <t>0.7184,0.0102,0.5151,0.0002</t>
+  </si>
+  <si>
+    <t>0.7320,0.0075,0.4726,0.0007</t>
+  </si>
+  <si>
+    <t>0.2261,0.0043,0.8853,0.0001</t>
+  </si>
+  <si>
+    <t>0.8696,0.0048,0.2578,0.0003</t>
+  </si>
+  <si>
+    <t>0.9008,0.0145,0.1306,0.0020</t>
+  </si>
+  <si>
+    <t>0.9754,0.0074,0.0261,0.0008</t>
+  </si>
+  <si>
+    <t>0.9419,0.0093,0.0745,0.0037</t>
+  </si>
+  <si>
+    <t>0.9676,0.0081,0.0332,0.0005</t>
+  </si>
+  <si>
+    <t>0.9139,0.0196,0.0840,0.0007</t>
+  </si>
+  <si>
+    <t>0.9616,0.0125,0.0344,0.0004</t>
+  </si>
+  <si>
+    <t>0.9402,0.0282,0.0293,0.0021</t>
+  </si>
+  <si>
+    <t>0.9616,0.0101,0.0276,0.0026</t>
+  </si>
+  <si>
+    <t>0.9778,0.0094,0.0043,0.0011</t>
+  </si>
+  <si>
+    <t>0.9659,0.0133,0.0041,0.0030</t>
+  </si>
+  <si>
+    <t>0.9655,0.0111,0.0038,0.0047</t>
+  </si>
+  <si>
+    <t>0.9922,0.0016,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9422,0.0147,0.0160,0.0094</t>
+  </si>
+  <si>
+    <t>0.9460,0.0172,0.0493,0.0022</t>
+  </si>
+  <si>
+    <t>0.9742,0.0027,0.0454,0.0007</t>
+  </si>
+  <si>
+    <t>0.9850,0.0029,0.0104,0.0006</t>
+  </si>
+  <si>
+    <t>0.9181,0.0081,0.1279,0.0008</t>
+  </si>
+  <si>
+    <t>0.8054,0.0263,0.2613,0.0037</t>
+  </si>
+  <si>
+    <t>0.5525,0.0396,0.5236,0.0031</t>
+  </si>
+  <si>
+    <t>0.9648,0.0035,0.0862,0.0001</t>
+  </si>
+  <si>
+    <t>0.2400,0.0069,0.9134,0.0001</t>
+  </si>
+  <si>
+    <t>0.9782,0.0008,0.0723,0.0001</t>
+  </si>
+  <si>
+    <t>0.9549,0.0049,0.0609,0.0000</t>
+  </si>
+  <si>
+    <t>0.9813,0.0014,0.0019,0.0077</t>
+  </si>
+  <si>
+    <t>0.9726,0.0060,0.0023,0.0046</t>
+  </si>
+  <si>
+    <t>0.9871,0.0023,0.0039,0.0018</t>
+  </si>
+  <si>
+    <t>0.9670,0.0081,0.0085,0.0070</t>
+  </si>
+  <si>
+    <t>0.9786,0.0017,0.0019,0.0067</t>
+  </si>
+  <si>
+    <t>0.9886,0.0008,0.0012,0.0042</t>
+  </si>
+  <si>
+    <t>0.9676,0.0055,0.0063,0.0080</t>
+  </si>
+  <si>
+    <t>0.9782,0.0024,0.0014,0.0073</t>
+  </si>
+  <si>
+    <t>0.9143,0.0176,0.1229,0.0032</t>
+  </si>
+  <si>
+    <t>0.9263,0.0288,0.0237,0.0057</t>
+  </si>
+  <si>
+    <t>0.9729,0.0058,0.0112,0.0024</t>
+  </si>
+  <si>
+    <t>0.2948,0.0087,0.7831,0.0001</t>
+  </si>
+  <si>
+    <t>0.2596,0.0100,0.8717,0.0002</t>
+  </si>
+  <si>
+    <t>0.8806,0.0499,0.0843,0.0010</t>
+  </si>
+  <si>
+    <t>0.2324,0.0034,0.9324,0.0000</t>
+  </si>
+  <si>
+    <t>0.9038,0.0084,0.1282,0.0002</t>
+  </si>
+  <si>
+    <t>0.2934,0.0035,0.9122,0.0001</t>
+  </si>
+  <si>
+    <t>0.8310,0.0070,0.3218,0.0001</t>
+  </si>
+  <si>
+    <t>0.9330,0.0078,0.1164,0.0021</t>
+  </si>
+  <si>
+    <t>0.9952,0.0011,0.0052,0.0000</t>
+  </si>
+  <si>
+    <t>0.9632,0.0033,0.0683,0.0005</t>
+  </si>
+  <si>
+    <t>0.9335,0.0189,0.0641,0.0022</t>
+  </si>
+  <si>
+    <t>0.9844,0.0050,0.0031,0.0019</t>
+  </si>
+  <si>
+    <t>0.9675,0.0058,0.0043,0.0080</t>
+  </si>
+  <si>
+    <t>0.9758,0.0046,0.0029,0.0046</t>
+  </si>
+  <si>
+    <t>0.9842,0.0057,0.0033,0.0013</t>
+  </si>
+  <si>
+    <t>0.9680,0.0044,0.0027,0.0101</t>
+  </si>
+  <si>
+    <t>0.9792,0.0038,0.0040,0.0041</t>
+  </si>
+  <si>
+    <t>0.9890,0.0010,0.0010,0.0032</t>
+  </si>
+  <si>
+    <t>0.9716,0.0071,0.0049,0.0056</t>
+  </si>
+  <si>
+    <t>0.5413,0.0718,0.4499,0.0006</t>
+  </si>
+  <si>
+    <t>0.8488,0.0146,0.1702,0.0001</t>
+  </si>
+  <si>
+    <t>0.0772,0.0289,0.9537,0.0004</t>
+  </si>
+  <si>
+    <t>0.8184,0.0071,0.3213,0.0007</t>
+  </si>
+  <si>
+    <t>0.7109,0.0083,0.4945,0.0002</t>
+  </si>
+  <si>
+    <t>0.8978,0.0091,0.1327,0.0061</t>
+  </si>
+  <si>
+    <t>0.9754,0.0031,0.0475,0.0003</t>
+  </si>
+  <si>
+    <t>0.9615,0.0007,0.1198,0.0001</t>
+  </si>
+  <si>
+    <t>0.9604,0.0053,0.0368,0.0035</t>
+  </si>
+  <si>
+    <t>0.9624,0.0044,0.0098,0.0079</t>
+  </si>
+  <si>
+    <t>0.9152,0.0097,0.0178,0.0414</t>
+  </si>
+  <si>
+    <t>0.8435,0.0030,0.0146,0.1241</t>
+  </si>
+  <si>
+    <t>0.9598,0.0014,0.0013,0.0240</t>
+  </si>
+  <si>
+    <t>0.9373,0.0128,0.0068,0.0112</t>
   </si>
 </sst>
 </file>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
